--- a/data/trans_camb/P1403-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1403-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>8,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,6</t>
+          <t>7,23</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 7,94</t>
+          <t>-0,19; 7,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 3,13</t>
+          <t>-4,4; 3,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 10,02</t>
+          <t>1,65; 9,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,5</t>
+          <t>4,08; 12,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 7,79</t>
+          <t>-0,8; 7,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 12,67</t>
+          <t>5,19; 12,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,33</t>
+          <t>3,25; 9,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,66</t>
+          <t>-1,15; 4,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 10,55</t>
+          <t>4,46; 9,87</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>45,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 58,14</t>
+          <t>-0,83; 57,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 23,03</t>
+          <t>-24,81; 25,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,35; 71,54</t>
+          <t>9,85; 71,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,01; 88,71</t>
+          <t>22,2; 94,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 53,81</t>
+          <t>-5,72; 52,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,24; 91,25</t>
+          <t>28,63; 87,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 65,14</t>
+          <t>18,52; 62,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 32,41</t>
+          <t>-6,86; 30,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,59; 73,3</t>
+          <t>26,06; 69,26</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>3,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 5,55</t>
+          <t>-0,43; 5,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,46</t>
+          <t>0,52; 6,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 6,53</t>
+          <t>2,08; 8,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 4,02</t>
+          <t>-3,27; 3,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 2,6</t>
+          <t>-4,96; 1,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,81</t>
+          <t>-2,15; 4,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,83</t>
+          <t>-0,99; 3,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,56</t>
+          <t>-1,3; 3,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 4,14</t>
+          <t>0,89; 5,35</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 51,91</t>
+          <t>-3,23; 53,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 61,73</t>
+          <t>3,63; 63,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,8; 57,19</t>
+          <t>15,0; 75,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 24,28</t>
+          <t>-16,44; 24,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 15,8</t>
+          <t>-24,24; 12,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 23,43</t>
+          <t>-10,49; 24,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 26,92</t>
+          <t>-5,83; 27,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 25,4</t>
+          <t>-8,5; 22,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 28,6</t>
+          <t>5,22; 38,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,74</t>
+          <t>7,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,13</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,98</t>
+          <t>3,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,89</t>
+          <t>-1,81; 6,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 5,37</t>
+          <t>-2,27; 4,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 11,01</t>
+          <t>3,04; 10,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 4,31</t>
+          <t>-4,71; 3,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 4,73</t>
+          <t>-3,48; 4,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 49,83</t>
+          <t>-3,78; 3,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,93</t>
+          <t>-1,49; 3,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,92</t>
+          <t>-1,67; 3,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 42,12</t>
+          <t>0,33; 5,64</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>-3,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 52,78</t>
+          <t>-13,64; 57,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 48,98</t>
+          <t>-14,82; 44,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,73; 102,65</t>
+          <t>19,9; 101,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 28,32</t>
+          <t>-24,04; 23,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 30,71</t>
+          <t>-17,96; 31,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 320,32</t>
+          <t>-19,42; 20,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 28,27</t>
+          <t>-9,35; 29,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 29,01</t>
+          <t>-10,51; 27,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 291,08</t>
+          <t>1,99; 40,56</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>6,66</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>6,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,88</t>
+          <t>3,15; 9,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 6,33</t>
+          <t>0,1; 6,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,9</t>
+          <t>3,75; 9,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 10,75</t>
+          <t>3,77; 10,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 4,47</t>
+          <t>-2,0; 4,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 9,97</t>
+          <t>3,97; 10,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,49</t>
+          <t>4,44; 9,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,37</t>
+          <t>-0,21; 4,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 9,05</t>
+          <t>4,73; 8,93</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,76; 88,1</t>
+          <t>21,9; 90,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 58,04</t>
+          <t>0,61; 56,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,87; 100,48</t>
+          <t>27,02; 88,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,21; 73,58</t>
+          <t>21,65; 76,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 30,23</t>
+          <t>-11,5; 32,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,44; 68,59</t>
+          <t>21,36; 70,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,82; 72,23</t>
+          <t>27,94; 71,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 33,26</t>
+          <t>-1,4; 33,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,04; 67,66</t>
+          <t>30,89; 67,15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>3,99</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>5,05</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,46</t>
+          <t>2,14; 5,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,8</t>
+          <t>0,33; 3,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,07</t>
+          <t>4,47; 7,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,0</t>
+          <t>2,11; 5,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,64</t>
+          <t>-1,12; 2,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 23,52</t>
+          <t>2,39; 5,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,16</t>
+          <t>2,66; 5,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,7</t>
+          <t>0,09; 2,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,71; 14,76</t>
+          <t>3,7; 6,18</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>13,87; 45,45</t>
+          <t>15,37; 45,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3,32; 31,33</t>
+          <t>2,37; 30,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8,39; 56,92</t>
+          <t>32,82; 65,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,71; 37,81</t>
+          <t>11,97; 36,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 16,6</t>
+          <t>-6,33; 17,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,13; 138,87</t>
+          <t>13,33; 35,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,9; 36,11</t>
+          <t>17,16; 35,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,81; 18,68</t>
+          <t>0,5; 18,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>23,88; 97,5</t>
+          <t>23,45; 43,09</t>
         </is>
       </c>
     </row>
